--- a/AAII_Financials/Yearly/SSEZY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSEZY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -709,16 +709,16 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>15496000</v>
+        <v>15926900</v>
       </c>
       <c r="E8" s="3">
-        <v>10679300</v>
+        <v>10976300</v>
       </c>
       <c r="F8" s="3">
-        <v>8468800</v>
+        <v>8704300</v>
       </c>
       <c r="G8" s="3">
-        <v>8436800</v>
+        <v>8671400</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
@@ -736,16 +736,16 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>15694100</v>
+        <v>16130500</v>
       </c>
       <c r="E9" s="3">
-        <v>5226600</v>
+        <v>5372000</v>
       </c>
       <c r="F9" s="3">
-        <v>5128800</v>
+        <v>5271400</v>
       </c>
       <c r="G9" s="3">
-        <v>5935400</v>
+        <v>6100500</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
@@ -763,16 +763,16 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>-198100</v>
+        <v>-203600</v>
       </c>
       <c r="E10" s="3">
-        <v>5452700</v>
+        <v>5604300</v>
       </c>
       <c r="F10" s="3">
-        <v>3340100</v>
+        <v>3433000</v>
       </c>
       <c r="G10" s="3">
-        <v>2501400</v>
+        <v>2571000</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -857,16 +857,16 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>161900</v>
+        <v>166400</v>
       </c>
       <c r="E14" s="3">
-        <v>-337200</v>
+        <v>-346600</v>
       </c>
       <c r="F14" s="3">
-        <v>-1017500</v>
+        <v>-1045800</v>
       </c>
       <c r="G14" s="3">
-        <v>260900</v>
+        <v>268200</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -921,16 +921,16 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>15677200</v>
+        <v>16113200</v>
       </c>
       <c r="E17" s="3">
-        <v>6016400</v>
+        <v>6183700</v>
       </c>
       <c r="F17" s="3">
-        <v>5173400</v>
+        <v>5317300</v>
       </c>
       <c r="G17" s="3">
-        <v>7238700</v>
+        <v>7440000</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>3</v>
@@ -948,16 +948,16 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-181300</v>
+        <v>-186300</v>
       </c>
       <c r="E18" s="3">
-        <v>4662900</v>
+        <v>4792600</v>
       </c>
       <c r="F18" s="3">
-        <v>3295400</v>
+        <v>3387000</v>
       </c>
       <c r="G18" s="3">
-        <v>1198200</v>
+        <v>1231500</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
@@ -988,16 +988,16 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>390900</v>
+        <v>401800</v>
       </c>
       <c r="E20" s="3">
-        <v>98900</v>
+        <v>101600</v>
       </c>
       <c r="F20" s="3">
-        <v>161300</v>
+        <v>165800</v>
       </c>
       <c r="G20" s="3">
-        <v>-16100</v>
+        <v>-16600</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
@@ -1015,13 +1015,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1005300</v>
+        <v>1035300</v>
       </c>
       <c r="E21" s="3">
-        <v>5138300</v>
+        <v>5282200</v>
       </c>
       <c r="F21" s="3">
-        <v>4248800</v>
+        <v>4369100</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>3</v>
@@ -1042,16 +1042,16 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>464700</v>
+        <v>477700</v>
       </c>
       <c r="E22" s="3">
-        <v>441800</v>
+        <v>454100</v>
       </c>
       <c r="F22" s="3">
-        <v>456900</v>
+        <v>469600</v>
       </c>
       <c r="G22" s="3">
-        <v>453100</v>
+        <v>465700</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
@@ -1069,16 +1069,16 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-255100</v>
+        <v>-262200</v>
       </c>
       <c r="E23" s="3">
-        <v>4320000</v>
+        <v>4440200</v>
       </c>
       <c r="F23" s="3">
-        <v>2999800</v>
+        <v>3083200</v>
       </c>
       <c r="G23" s="3">
-        <v>729000</v>
+        <v>749200</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>3</v>
@@ -1096,16 +1096,16 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-136500</v>
+        <v>-140300</v>
       </c>
       <c r="E24" s="3">
-        <v>1095200</v>
+        <v>1125700</v>
       </c>
       <c r="F24" s="3">
-        <v>278300</v>
+        <v>286000</v>
       </c>
       <c r="G24" s="3">
-        <v>150700</v>
+        <v>154900</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
@@ -1150,16 +1150,16 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-118600</v>
+        <v>-121900</v>
       </c>
       <c r="E26" s="3">
-        <v>3224800</v>
+        <v>3314500</v>
       </c>
       <c r="F26" s="3">
-        <v>2721500</v>
+        <v>2797200</v>
       </c>
       <c r="G26" s="3">
-        <v>578200</v>
+        <v>594300</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>3</v>
@@ -1177,16 +1177,16 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-196000</v>
+        <v>-201500</v>
       </c>
       <c r="E27" s="3">
-        <v>3161900</v>
+        <v>3249800</v>
       </c>
       <c r="F27" s="3">
-        <v>2663700</v>
+        <v>2737800</v>
       </c>
       <c r="G27" s="3">
-        <v>520600</v>
+        <v>535000</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>3</v>
@@ -1231,16 +1231,16 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>43400</v>
+        <v>44600</v>
       </c>
       <c r="E29" s="3">
-        <v>598800</v>
+        <v>615500</v>
       </c>
       <c r="F29" s="3">
-        <v>198200</v>
+        <v>203800</v>
       </c>
       <c r="G29" s="3">
-        <v>-593800</v>
+        <v>-610300</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>3</v>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-390900</v>
+        <v>-401800</v>
       </c>
       <c r="E32" s="3">
-        <v>-98900</v>
+        <v>-101600</v>
       </c>
       <c r="F32" s="3">
-        <v>-161300</v>
+        <v>-165800</v>
       </c>
       <c r="G32" s="3">
-        <v>16100</v>
+        <v>16600</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
@@ -1339,16 +1339,16 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-152600</v>
+        <v>-156800</v>
       </c>
       <c r="E33" s="3">
-        <v>3760800</v>
+        <v>3865300</v>
       </c>
       <c r="F33" s="3">
-        <v>2861900</v>
+        <v>2941500</v>
       </c>
       <c r="G33" s="3">
-        <v>-73200</v>
+        <v>-75200</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>3</v>
@@ -1393,16 +1393,16 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-152600</v>
+        <v>-156800</v>
       </c>
       <c r="E35" s="3">
-        <v>3760800</v>
+        <v>3865300</v>
       </c>
       <c r="F35" s="3">
-        <v>2861900</v>
+        <v>2941500</v>
       </c>
       <c r="G35" s="3">
-        <v>-73200</v>
+        <v>-75200</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>3</v>
@@ -1478,16 +1478,16 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1106400</v>
+        <v>1137100</v>
       </c>
       <c r="E41" s="3">
-        <v>1301800</v>
+        <v>1338000</v>
       </c>
       <c r="F41" s="3">
-        <v>1985200</v>
+        <v>2040400</v>
       </c>
       <c r="G41" s="3">
-        <v>204200</v>
+        <v>209900</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
@@ -1532,16 +1532,16 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>6899100</v>
+        <v>7091000</v>
       </c>
       <c r="E43" s="3">
-        <v>2537300</v>
+        <v>2607800</v>
       </c>
       <c r="F43" s="3">
-        <v>1625400</v>
+        <v>1670600</v>
       </c>
       <c r="G43" s="3">
-        <v>1740900</v>
+        <v>1789300</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
@@ -1559,16 +1559,16 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>979800</v>
+        <v>1007100</v>
       </c>
       <c r="E44" s="3">
-        <v>330700</v>
+        <v>339900</v>
       </c>
       <c r="F44" s="3">
-        <v>291400</v>
+        <v>299500</v>
       </c>
       <c r="G44" s="3">
-        <v>215900</v>
+        <v>221900</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
@@ -1586,16 +1586,16 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2683500</v>
+        <v>2758200</v>
       </c>
       <c r="E45" s="3">
-        <v>4436000</v>
+        <v>4559400</v>
       </c>
       <c r="F45" s="3">
-        <v>1706600</v>
+        <v>1754000</v>
       </c>
       <c r="G45" s="3">
-        <v>2151400</v>
+        <v>2211300</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
@@ -1613,16 +1613,16 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>7153100</v>
+        <v>7352000</v>
       </c>
       <c r="E46" s="3">
-        <v>8605800</v>
+        <v>8845100</v>
       </c>
       <c r="F46" s="3">
-        <v>5608600</v>
+        <v>5764600</v>
       </c>
       <c r="G46" s="3">
-        <v>4312400</v>
+        <v>4432400</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>3</v>
@@ -1640,16 +1640,16 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>4048000</v>
+        <v>4160500</v>
       </c>
       <c r="E47" s="3">
-        <v>2631900</v>
+        <v>2705100</v>
       </c>
       <c r="F47" s="3">
-        <v>2874800</v>
+        <v>2954800</v>
       </c>
       <c r="G47" s="3">
-        <v>3470100</v>
+        <v>3566600</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
@@ -1667,16 +1667,16 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>38200300</v>
+        <v>39262600</v>
       </c>
       <c r="E48" s="3">
-        <v>18136000</v>
+        <v>18640300</v>
       </c>
       <c r="F48" s="3">
-        <v>16443300</v>
+        <v>16900600</v>
       </c>
       <c r="G48" s="3">
-        <v>15897900</v>
+        <v>16340000</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
@@ -1694,16 +1694,16 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>4863900</v>
+        <v>4999200</v>
       </c>
       <c r="E49" s="3">
-        <v>1399100</v>
+        <v>1438100</v>
       </c>
       <c r="F49" s="3">
-        <v>1043700</v>
+        <v>1072700</v>
       </c>
       <c r="G49" s="3">
-        <v>1366400</v>
+        <v>1404400</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>3</v>
@@ -1775,16 +1775,16 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>976500</v>
+        <v>1003600</v>
       </c>
       <c r="E52" s="3">
-        <v>1186800</v>
+        <v>1219800</v>
       </c>
       <c r="F52" s="3">
-        <v>816100</v>
+        <v>838800</v>
       </c>
       <c r="G52" s="3">
-        <v>1045100</v>
+        <v>1074100</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
@@ -1829,16 +1829,16 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>33709600</v>
+        <v>34647000</v>
       </c>
       <c r="E54" s="3">
-        <v>31959600</v>
+        <v>32848400</v>
       </c>
       <c r="F54" s="3">
-        <v>26786500</v>
+        <v>27531400</v>
       </c>
       <c r="G54" s="3">
-        <v>26091900</v>
+        <v>26817500</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
@@ -1882,16 +1882,16 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4160000</v>
+        <v>4275700</v>
       </c>
       <c r="E57" s="3">
-        <v>1141000</v>
+        <v>1172700</v>
       </c>
       <c r="F57" s="3">
-        <v>537600</v>
+        <v>552500</v>
       </c>
       <c r="G57" s="3">
-        <v>512600</v>
+        <v>526900</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
@@ -1909,16 +1909,16 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2258600</v>
+        <v>2321400</v>
       </c>
       <c r="E58" s="3">
-        <v>1477300</v>
+        <v>1518400</v>
       </c>
       <c r="F58" s="3">
-        <v>1163200</v>
+        <v>1195500</v>
       </c>
       <c r="G58" s="3">
-        <v>2440100</v>
+        <v>2508000</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
@@ -1936,16 +1936,16 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2791100</v>
+        <v>2868700</v>
       </c>
       <c r="E59" s="3">
-        <v>3160700</v>
+        <v>3248600</v>
       </c>
       <c r="F59" s="3">
-        <v>2652800</v>
+        <v>2726500</v>
       </c>
       <c r="G59" s="3">
-        <v>3508500</v>
+        <v>3606100</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
@@ -1963,16 +1963,16 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>5911500</v>
+        <v>6075900</v>
       </c>
       <c r="E60" s="3">
-        <v>5779000</v>
+        <v>5939700</v>
       </c>
       <c r="F60" s="3">
-        <v>4353500</v>
+        <v>4474600</v>
       </c>
       <c r="G60" s="3">
-        <v>6461300</v>
+        <v>6641000</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>3</v>
@@ -1990,16 +1990,16 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8981100</v>
+        <v>9230800</v>
       </c>
       <c r="E61" s="3">
-        <v>9768400</v>
+        <v>10040000</v>
       </c>
       <c r="F61" s="3">
-        <v>10511600</v>
+        <v>10803900</v>
       </c>
       <c r="G61" s="3">
-        <v>10179700</v>
+        <v>10462800</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2017,16 +2017,16 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>6254000</v>
+        <v>6427900</v>
       </c>
       <c r="E62" s="3">
-        <v>5031300</v>
+        <v>5171200</v>
       </c>
       <c r="F62" s="3">
-        <v>3632800</v>
+        <v>3733900</v>
       </c>
       <c r="G62" s="3">
-        <v>3347000</v>
+        <v>3440100</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -2125,16 +2125,16 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>20760900</v>
+        <v>21338300</v>
       </c>
       <c r="E66" s="3">
-        <v>20628900</v>
+        <v>21202600</v>
       </c>
       <c r="F66" s="3">
-        <v>18498000</v>
+        <v>19012400</v>
       </c>
       <c r="G66" s="3">
-        <v>19988100</v>
+        <v>20543900</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
@@ -2273,16 +2273,16 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>8328800</v>
+        <v>8560400</v>
       </c>
       <c r="E72" s="3">
-        <v>8220800</v>
+        <v>8449500</v>
       </c>
       <c r="F72" s="3">
-        <v>4925600</v>
+        <v>5062500</v>
       </c>
       <c r="G72" s="3">
-        <v>3047400</v>
+        <v>3132200</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
@@ -2381,16 +2381,16 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>12948600</v>
+        <v>13308700</v>
       </c>
       <c r="E76" s="3">
-        <v>11330600</v>
+        <v>11645700</v>
       </c>
       <c r="F76" s="3">
-        <v>8288600</v>
+        <v>8519100</v>
       </c>
       <c r="G76" s="3">
-        <v>6103900</v>
+        <v>6273600</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>3</v>
@@ -2467,16 +2467,16 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-152600</v>
+        <v>-156800</v>
       </c>
       <c r="E81" s="3">
-        <v>3760800</v>
+        <v>3865300</v>
       </c>
       <c r="F81" s="3">
-        <v>2861900</v>
+        <v>2941500</v>
       </c>
       <c r="G81" s="3">
-        <v>-73200</v>
+        <v>-75200</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>3</v>
@@ -2507,13 +2507,13 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>794900</v>
+        <v>817000</v>
       </c>
       <c r="E83" s="3">
-        <v>376100</v>
+        <v>386600</v>
       </c>
       <c r="F83" s="3">
-        <v>791400</v>
+        <v>813400</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>3</v>
@@ -2669,13 +2669,13 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1853500</v>
+        <v>1905000</v>
       </c>
       <c r="E89" s="3">
-        <v>2019600</v>
+        <v>2075700</v>
       </c>
       <c r="F89" s="3">
-        <v>2254400</v>
+        <v>2317100</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>3</v>
@@ -2709,13 +2709,13 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1835700</v>
+        <v>-1886800</v>
       </c>
       <c r="E91" s="3">
-        <v>-1580000</v>
+        <v>-1624000</v>
       </c>
       <c r="F91" s="3">
-        <v>-1222000</v>
+        <v>-1256000</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>3</v>
@@ -2790,13 +2790,13 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-3677600</v>
+        <v>-3779900</v>
       </c>
       <c r="E94" s="3">
-        <v>-924100</v>
+        <v>-949800</v>
       </c>
       <c r="F94" s="3">
-        <v>550500</v>
+        <v>565800</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>3</v>
@@ -2830,13 +2830,13 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-588400</v>
+        <v>-604800</v>
       </c>
       <c r="E96" s="3">
-        <v>-628500</v>
+        <v>-646000</v>
       </c>
       <c r="F96" s="3">
-        <v>-989300</v>
+        <v>-1016800</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
@@ -2938,13 +2938,13 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1628800</v>
+        <v>1674100</v>
       </c>
       <c r="E100" s="3">
-        <v>-1778900</v>
+        <v>-1828400</v>
       </c>
       <c r="F100" s="3">
-        <v>-1023900</v>
+        <v>-1052300</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>3</v>
@@ -2992,13 +2992,13 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-195400</v>
+        <v>-200800</v>
       </c>
       <c r="E102" s="3">
-        <v>-683400</v>
+        <v>-702500</v>
       </c>
       <c r="F102" s="3">
-        <v>1781000</v>
+        <v>1830500</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/SSEZY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSEZY_YR_FIN.xlsx
@@ -709,16 +709,16 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>15926900</v>
+        <v>15983200</v>
       </c>
       <c r="E8" s="3">
-        <v>10976300</v>
+        <v>11015100</v>
       </c>
       <c r="F8" s="3">
-        <v>8704300</v>
+        <v>8735100</v>
       </c>
       <c r="G8" s="3">
-        <v>8671400</v>
+        <v>8702100</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
@@ -736,16 +736,16 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>16130500</v>
+        <v>16187600</v>
       </c>
       <c r="E9" s="3">
-        <v>5372000</v>
+        <v>5391000</v>
       </c>
       <c r="F9" s="3">
-        <v>5271400</v>
+        <v>5290000</v>
       </c>
       <c r="G9" s="3">
-        <v>6100500</v>
+        <v>6122000</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
@@ -763,16 +763,16 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>-203600</v>
+        <v>-204400</v>
       </c>
       <c r="E10" s="3">
-        <v>5604300</v>
+        <v>5624100</v>
       </c>
       <c r="F10" s="3">
-        <v>3433000</v>
+        <v>3445100</v>
       </c>
       <c r="G10" s="3">
-        <v>2571000</v>
+        <v>2580100</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -857,16 +857,16 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>166400</v>
+        <v>167000</v>
       </c>
       <c r="E14" s="3">
-        <v>-346600</v>
+        <v>-347800</v>
       </c>
       <c r="F14" s="3">
-        <v>-1045800</v>
+        <v>-1049500</v>
       </c>
       <c r="G14" s="3">
-        <v>268200</v>
+        <v>269100</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -921,16 +921,16 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>16113200</v>
+        <v>16170200</v>
       </c>
       <c r="E17" s="3">
-        <v>6183700</v>
+        <v>6205600</v>
       </c>
       <c r="F17" s="3">
-        <v>5317300</v>
+        <v>5336100</v>
       </c>
       <c r="G17" s="3">
-        <v>7440000</v>
+        <v>7466300</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>3</v>
@@ -948,16 +948,16 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-186300</v>
+        <v>-187000</v>
       </c>
       <c r="E18" s="3">
-        <v>4792600</v>
+        <v>4809500</v>
       </c>
       <c r="F18" s="3">
-        <v>3387000</v>
+        <v>3399000</v>
       </c>
       <c r="G18" s="3">
-        <v>1231500</v>
+        <v>1235800</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
@@ -988,13 +988,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>401800</v>
+        <v>403200</v>
       </c>
       <c r="E20" s="3">
-        <v>101600</v>
+        <v>102000</v>
       </c>
       <c r="F20" s="3">
-        <v>165800</v>
+        <v>166300</v>
       </c>
       <c r="G20" s="3">
         <v>-16600</v>
@@ -1015,13 +1015,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1035300</v>
+        <v>1032500</v>
       </c>
       <c r="E21" s="3">
-        <v>5282200</v>
+        <v>5297800</v>
       </c>
       <c r="F21" s="3">
-        <v>4369100</v>
+        <v>4378100</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>3</v>
@@ -1042,16 +1042,16 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>477700</v>
+        <v>479300</v>
       </c>
       <c r="E22" s="3">
-        <v>454100</v>
+        <v>455700</v>
       </c>
       <c r="F22" s="3">
-        <v>469600</v>
+        <v>471300</v>
       </c>
       <c r="G22" s="3">
-        <v>465700</v>
+        <v>467300</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
@@ -1069,16 +1069,16 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-262200</v>
+        <v>-263100</v>
       </c>
       <c r="E23" s="3">
-        <v>4440200</v>
+        <v>4455900</v>
       </c>
       <c r="F23" s="3">
-        <v>3083200</v>
+        <v>3094100</v>
       </c>
       <c r="G23" s="3">
-        <v>749200</v>
+        <v>751900</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>3</v>
@@ -1096,16 +1096,16 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-140300</v>
+        <v>-140800</v>
       </c>
       <c r="E24" s="3">
-        <v>1125700</v>
+        <v>1129600</v>
       </c>
       <c r="F24" s="3">
-        <v>286000</v>
+        <v>287000</v>
       </c>
       <c r="G24" s="3">
-        <v>154900</v>
+        <v>155500</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
@@ -1150,16 +1150,16 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-121900</v>
+        <v>-122300</v>
       </c>
       <c r="E26" s="3">
-        <v>3314500</v>
+        <v>3326200</v>
       </c>
       <c r="F26" s="3">
-        <v>2797200</v>
+        <v>2807100</v>
       </c>
       <c r="G26" s="3">
-        <v>594300</v>
+        <v>596400</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>3</v>
@@ -1177,16 +1177,16 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-201500</v>
+        <v>-202200</v>
       </c>
       <c r="E27" s="3">
-        <v>3249800</v>
+        <v>3261300</v>
       </c>
       <c r="F27" s="3">
-        <v>2737800</v>
+        <v>2747500</v>
       </c>
       <c r="G27" s="3">
-        <v>535000</v>
+        <v>536900</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>3</v>
@@ -1231,16 +1231,16 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>44600</v>
+        <v>44800</v>
       </c>
       <c r="E29" s="3">
-        <v>615500</v>
+        <v>617700</v>
       </c>
       <c r="F29" s="3">
-        <v>203800</v>
+        <v>204500</v>
       </c>
       <c r="G29" s="3">
-        <v>-610300</v>
+        <v>-612400</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>3</v>
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-401800</v>
+        <v>-403200</v>
       </c>
       <c r="E32" s="3">
-        <v>-101600</v>
+        <v>-102000</v>
       </c>
       <c r="F32" s="3">
-        <v>-165800</v>
+        <v>-166300</v>
       </c>
       <c r="G32" s="3">
         <v>16600</v>
@@ -1339,16 +1339,16 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-156800</v>
+        <v>-157400</v>
       </c>
       <c r="E33" s="3">
-        <v>3865300</v>
+        <v>3879000</v>
       </c>
       <c r="F33" s="3">
-        <v>2941500</v>
+        <v>2951900</v>
       </c>
       <c r="G33" s="3">
-        <v>-75200</v>
+        <v>-75500</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>3</v>
@@ -1393,16 +1393,16 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-156800</v>
+        <v>-157400</v>
       </c>
       <c r="E35" s="3">
-        <v>3865300</v>
+        <v>3879000</v>
       </c>
       <c r="F35" s="3">
-        <v>2941500</v>
+        <v>2951900</v>
       </c>
       <c r="G35" s="3">
-        <v>-75200</v>
+        <v>-75500</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>3</v>
@@ -1478,16 +1478,16 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1137100</v>
+        <v>1141200</v>
       </c>
       <c r="E41" s="3">
-        <v>1338000</v>
+        <v>1342700</v>
       </c>
       <c r="F41" s="3">
-        <v>2040400</v>
+        <v>2047600</v>
       </c>
       <c r="G41" s="3">
-        <v>209900</v>
+        <v>210600</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
@@ -1532,16 +1532,16 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>7091000</v>
+        <v>7116000</v>
       </c>
       <c r="E43" s="3">
-        <v>2607800</v>
+        <v>2617100</v>
       </c>
       <c r="F43" s="3">
-        <v>1670600</v>
+        <v>1676500</v>
       </c>
       <c r="G43" s="3">
-        <v>1789300</v>
+        <v>1795700</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
@@ -1559,16 +1559,16 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1007100</v>
+        <v>1010600</v>
       </c>
       <c r="E44" s="3">
-        <v>339900</v>
+        <v>341100</v>
       </c>
       <c r="F44" s="3">
-        <v>299500</v>
+        <v>300600</v>
       </c>
       <c r="G44" s="3">
-        <v>221900</v>
+        <v>222700</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
@@ -1586,16 +1586,16 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2758200</v>
+        <v>2767900</v>
       </c>
       <c r="E45" s="3">
-        <v>4559400</v>
+        <v>4575500</v>
       </c>
       <c r="F45" s="3">
-        <v>1754000</v>
+        <v>1760200</v>
       </c>
       <c r="G45" s="3">
-        <v>2211300</v>
+        <v>2219100</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
@@ -1613,16 +1613,16 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>7352000</v>
+        <v>7378000</v>
       </c>
       <c r="E46" s="3">
-        <v>8845100</v>
+        <v>8876400</v>
       </c>
       <c r="F46" s="3">
-        <v>5764600</v>
+        <v>5785000</v>
       </c>
       <c r="G46" s="3">
-        <v>4432400</v>
+        <v>4448100</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>3</v>
@@ -1640,16 +1640,16 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>4160500</v>
+        <v>4175200</v>
       </c>
       <c r="E47" s="3">
-        <v>2705100</v>
+        <v>2714700</v>
       </c>
       <c r="F47" s="3">
-        <v>2954800</v>
+        <v>2965200</v>
       </c>
       <c r="G47" s="3">
-        <v>3566600</v>
+        <v>3579200</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
@@ -1667,16 +1667,16 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>39262600</v>
+        <v>39401500</v>
       </c>
       <c r="E48" s="3">
-        <v>18640300</v>
+        <v>18706200</v>
       </c>
       <c r="F48" s="3">
-        <v>16900600</v>
+        <v>16960300</v>
       </c>
       <c r="G48" s="3">
-        <v>16340000</v>
+        <v>16397800</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
@@ -1694,16 +1694,16 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>4999200</v>
+        <v>5016800</v>
       </c>
       <c r="E49" s="3">
-        <v>1438100</v>
+        <v>1443100</v>
       </c>
       <c r="F49" s="3">
-        <v>1072700</v>
+        <v>1076500</v>
       </c>
       <c r="G49" s="3">
-        <v>1404400</v>
+        <v>1409400</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>3</v>
@@ -1775,16 +1775,16 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1003600</v>
+        <v>1007200</v>
       </c>
       <c r="E52" s="3">
-        <v>1219800</v>
+        <v>1224100</v>
       </c>
       <c r="F52" s="3">
-        <v>838800</v>
+        <v>841700</v>
       </c>
       <c r="G52" s="3">
-        <v>1074100</v>
+        <v>1077900</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
@@ -1829,16 +1829,16 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>34647000</v>
+        <v>34769600</v>
       </c>
       <c r="E54" s="3">
-        <v>32848400</v>
+        <v>32964500</v>
       </c>
       <c r="F54" s="3">
-        <v>27531400</v>
+        <v>27628800</v>
       </c>
       <c r="G54" s="3">
-        <v>26817500</v>
+        <v>26912400</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
@@ -1882,16 +1882,16 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4275700</v>
+        <v>4290800</v>
       </c>
       <c r="E57" s="3">
-        <v>1172700</v>
+        <v>1176900</v>
       </c>
       <c r="F57" s="3">
-        <v>552500</v>
+        <v>554500</v>
       </c>
       <c r="G57" s="3">
-        <v>526900</v>
+        <v>528700</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
@@ -1909,16 +1909,16 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2321400</v>
+        <v>2329700</v>
       </c>
       <c r="E58" s="3">
-        <v>1518400</v>
+        <v>1523800</v>
       </c>
       <c r="F58" s="3">
-        <v>1195500</v>
+        <v>1199800</v>
       </c>
       <c r="G58" s="3">
-        <v>2508000</v>
+        <v>2516900</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
@@ -1936,16 +1936,16 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2868700</v>
+        <v>2878900</v>
       </c>
       <c r="E59" s="3">
-        <v>3248600</v>
+        <v>3260100</v>
       </c>
       <c r="F59" s="3">
-        <v>2726500</v>
+        <v>2736200</v>
       </c>
       <c r="G59" s="3">
-        <v>3606100</v>
+        <v>3618900</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
@@ -1963,16 +1963,16 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>6075900</v>
+        <v>6097300</v>
       </c>
       <c r="E60" s="3">
-        <v>5939700</v>
+        <v>5960700</v>
       </c>
       <c r="F60" s="3">
-        <v>4474600</v>
+        <v>4490400</v>
       </c>
       <c r="G60" s="3">
-        <v>6641000</v>
+        <v>6664500</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>3</v>
@@ -1990,16 +1990,16 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>9230800</v>
+        <v>9263500</v>
       </c>
       <c r="E61" s="3">
-        <v>10040000</v>
+        <v>10075500</v>
       </c>
       <c r="F61" s="3">
-        <v>10803900</v>
+        <v>10842100</v>
       </c>
       <c r="G61" s="3">
-        <v>10462800</v>
+        <v>10499800</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2017,16 +2017,16 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>6427900</v>
+        <v>6450600</v>
       </c>
       <c r="E62" s="3">
-        <v>5171200</v>
+        <v>5189500</v>
       </c>
       <c r="F62" s="3">
-        <v>3733900</v>
+        <v>3747100</v>
       </c>
       <c r="G62" s="3">
-        <v>3440100</v>
+        <v>3452300</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -2125,16 +2125,16 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>21338300</v>
+        <v>21413800</v>
       </c>
       <c r="E66" s="3">
-        <v>21202600</v>
+        <v>21277600</v>
       </c>
       <c r="F66" s="3">
-        <v>19012400</v>
+        <v>19079600</v>
       </c>
       <c r="G66" s="3">
-        <v>20543900</v>
+        <v>20616600</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
@@ -2273,16 +2273,16 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>8560400</v>
+        <v>8590700</v>
       </c>
       <c r="E72" s="3">
-        <v>8449500</v>
+        <v>8479300</v>
       </c>
       <c r="F72" s="3">
-        <v>5062500</v>
+        <v>5080400</v>
       </c>
       <c r="G72" s="3">
-        <v>3132200</v>
+        <v>3143200</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
@@ -2381,16 +2381,16 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>13308700</v>
+        <v>13355800</v>
       </c>
       <c r="E76" s="3">
-        <v>11645700</v>
+        <v>11686900</v>
       </c>
       <c r="F76" s="3">
-        <v>8519100</v>
+        <v>8549200</v>
       </c>
       <c r="G76" s="3">
-        <v>6273600</v>
+        <v>6295800</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>3</v>
@@ -2467,16 +2467,16 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-156800</v>
+        <v>-157400</v>
       </c>
       <c r="E81" s="3">
-        <v>3865300</v>
+        <v>3879000</v>
       </c>
       <c r="F81" s="3">
-        <v>2941500</v>
+        <v>2951900</v>
       </c>
       <c r="G81" s="3">
-        <v>-75200</v>
+        <v>-75500</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>3</v>
@@ -2507,13 +2507,13 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>817000</v>
+        <v>819800</v>
       </c>
       <c r="E83" s="3">
-        <v>386600</v>
+        <v>388000</v>
       </c>
       <c r="F83" s="3">
-        <v>813400</v>
+        <v>816300</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>3</v>
@@ -2669,13 +2669,13 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1905000</v>
+        <v>1911700</v>
       </c>
       <c r="E89" s="3">
-        <v>2075700</v>
+        <v>2083100</v>
       </c>
       <c r="F89" s="3">
-        <v>2317100</v>
+        <v>2325300</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>3</v>
@@ -2709,13 +2709,13 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1886800</v>
+        <v>-1893400</v>
       </c>
       <c r="E91" s="3">
-        <v>-1624000</v>
+        <v>-1629700</v>
       </c>
       <c r="F91" s="3">
-        <v>-1256000</v>
+        <v>-1260400</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>3</v>
@@ -2790,13 +2790,13 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-3779900</v>
+        <v>-3793300</v>
       </c>
       <c r="E94" s="3">
-        <v>-949800</v>
+        <v>-953200</v>
       </c>
       <c r="F94" s="3">
-        <v>565800</v>
+        <v>567800</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>3</v>
@@ -2830,13 +2830,13 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-604800</v>
+        <v>-606900</v>
       </c>
       <c r="E96" s="3">
-        <v>-646000</v>
+        <v>-648300</v>
       </c>
       <c r="F96" s="3">
-        <v>-1016800</v>
+        <v>-1020400</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
@@ -2938,13 +2938,13 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1674100</v>
+        <v>1680000</v>
       </c>
       <c r="E100" s="3">
-        <v>-1828400</v>
+        <v>-1834800</v>
       </c>
       <c r="F100" s="3">
-        <v>-1052300</v>
+        <v>-1056100</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>3</v>
@@ -2992,13 +2992,13 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-200800</v>
+        <v>-201500</v>
       </c>
       <c r="E102" s="3">
-        <v>-702500</v>
+        <v>-704900</v>
       </c>
       <c r="F102" s="3">
-        <v>1830500</v>
+        <v>1837000</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/SSEZY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSEZY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="92">
   <si>
     <t>SSEZY</t>
   </si>
@@ -656,72 +656,75 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45016</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44651</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44286</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43921</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>15983200</v>
+        <v>13721900</v>
       </c>
       <c r="E8" s="3">
-        <v>11015100</v>
+        <v>16390300</v>
       </c>
       <c r="F8" s="3">
-        <v>8735100</v>
+        <v>11295700</v>
       </c>
       <c r="G8" s="3">
-        <v>8702100</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
+        <v>8957600</v>
+      </c>
+      <c r="H8" s="3">
+        <v>8923700</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
@@ -729,26 +732,29 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>16187600</v>
+        <v>8013600</v>
       </c>
       <c r="E9" s="3">
-        <v>5391000</v>
+        <v>16599900</v>
       </c>
       <c r="F9" s="3">
-        <v>5290000</v>
+        <v>5528300</v>
       </c>
       <c r="G9" s="3">
-        <v>6122000</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
+        <v>5424800</v>
+      </c>
+      <c r="H9" s="3">
+        <v>6278000</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>3</v>
@@ -756,26 +762,29 @@
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>-204400</v>
+        <v>5708300</v>
       </c>
       <c r="E10" s="3">
-        <v>5624100</v>
+        <v>-209600</v>
       </c>
       <c r="F10" s="3">
-        <v>3445100</v>
+        <v>5767400</v>
       </c>
       <c r="G10" s="3">
-        <v>2580100</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
+        <v>3532800</v>
+      </c>
+      <c r="H10" s="3">
+        <v>2645800</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>3</v>
@@ -783,9 +792,12 @@
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -797,8 +809,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -823,9 +836,12 @@
       <c r="J12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -850,26 +866,29 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>167000</v>
+        <v>518100</v>
       </c>
       <c r="E14" s="3">
-        <v>-347800</v>
+        <v>304600</v>
       </c>
       <c r="F14" s="3">
-        <v>-1049500</v>
+        <v>-400200</v>
       </c>
       <c r="G14" s="3">
-        <v>269100</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+        <v>-1076300</v>
+      </c>
+      <c r="H14" s="3">
+        <v>276000</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -877,9 +896,12 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -904,9 +926,12 @@
       <c r="J15" s="3">
         <v>0</v>
       </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -915,25 +940,26 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>16170200</v>
+        <v>10299100</v>
       </c>
       <c r="E17" s="3">
-        <v>6205600</v>
+        <v>16582000</v>
       </c>
       <c r="F17" s="3">
-        <v>5336100</v>
+        <v>6363600</v>
       </c>
       <c r="G17" s="3">
-        <v>7466300</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
+        <v>5472000</v>
+      </c>
+      <c r="H17" s="3">
+        <v>7656400</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>3</v>
@@ -941,26 +967,29 @@
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-187000</v>
+        <v>3422900</v>
       </c>
       <c r="E18" s="3">
-        <v>4809500</v>
+        <v>-191700</v>
       </c>
       <c r="F18" s="3">
-        <v>3399000</v>
+        <v>4932000</v>
       </c>
       <c r="G18" s="3">
-        <v>1235800</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
+        <v>3485600</v>
+      </c>
+      <c r="H18" s="3">
+        <v>1267300</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>3</v>
@@ -968,9 +997,12 @@
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -982,25 +1014,26 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>403200</v>
+        <v>235800</v>
       </c>
       <c r="E20" s="3">
-        <v>102000</v>
+        <v>413500</v>
       </c>
       <c r="F20" s="3">
-        <v>166300</v>
+        <v>104600</v>
       </c>
       <c r="G20" s="3">
-        <v>-16600</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
+        <v>170600</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-17100</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
@@ -1008,23 +1041,26 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1032500</v>
+        <v>4785900</v>
       </c>
       <c r="E21" s="3">
-        <v>5297800</v>
+        <v>1062600</v>
       </c>
       <c r="F21" s="3">
-        <v>4378100</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
+        <v>5434500</v>
+      </c>
+      <c r="G21" s="3">
+        <v>4493300</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
@@ -1035,26 +1071,29 @@
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>479300</v>
+        <v>384600</v>
       </c>
       <c r="E22" s="3">
-        <v>455700</v>
+        <v>491600</v>
       </c>
       <c r="F22" s="3">
-        <v>471300</v>
+        <v>467300</v>
       </c>
       <c r="G22" s="3">
-        <v>467300</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
+        <v>483300</v>
+      </c>
+      <c r="H22" s="3">
+        <v>479200</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
@@ -1062,26 +1101,29 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-263100</v>
+        <v>3274100</v>
       </c>
       <c r="E23" s="3">
-        <v>4455900</v>
+        <v>-269800</v>
       </c>
       <c r="F23" s="3">
-        <v>3094100</v>
+        <v>4569300</v>
       </c>
       <c r="G23" s="3">
-        <v>751900</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
+        <v>3172900</v>
+      </c>
+      <c r="H23" s="3">
+        <v>771000</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>3</v>
@@ -1089,26 +1131,29 @@
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-140800</v>
+        <v>801400</v>
       </c>
       <c r="E24" s="3">
-        <v>1129600</v>
+        <v>-144300</v>
       </c>
       <c r="F24" s="3">
-        <v>287000</v>
+        <v>1158400</v>
       </c>
       <c r="G24" s="3">
-        <v>155500</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
+        <v>294300</v>
+      </c>
+      <c r="H24" s="3">
+        <v>159400</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
@@ -1116,9 +1161,12 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1143,26 +1191,29 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-122300</v>
+        <v>2472700</v>
       </c>
       <c r="E26" s="3">
-        <v>3326200</v>
+        <v>-125400</v>
       </c>
       <c r="F26" s="3">
-        <v>2807100</v>
+        <v>3410900</v>
       </c>
       <c r="G26" s="3">
-        <v>596400</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
+        <v>2878600</v>
+      </c>
+      <c r="H26" s="3">
+        <v>611600</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>3</v>
@@ -1170,26 +1221,29 @@
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-202200</v>
+        <v>2244500</v>
       </c>
       <c r="E27" s="3">
-        <v>3261300</v>
+        <v>-207300</v>
       </c>
       <c r="F27" s="3">
-        <v>2747500</v>
+        <v>3344400</v>
       </c>
       <c r="G27" s="3">
-        <v>536900</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
+        <v>2817400</v>
+      </c>
+      <c r="H27" s="3">
+        <v>550600</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>3</v>
@@ -1197,9 +1251,12 @@
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1224,26 +1281,29 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>44800</v>
+        <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>617700</v>
+        <v>45900</v>
       </c>
       <c r="F29" s="3">
-        <v>204500</v>
+        <v>633400</v>
       </c>
       <c r="G29" s="3">
-        <v>-612400</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>3</v>
+        <v>209700</v>
+      </c>
+      <c r="H29" s="3">
+        <v>-628000</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>3</v>
@@ -1251,9 +1311,12 @@
       <c r="J29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1278,9 +1341,12 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1305,26 +1371,29 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-403200</v>
+        <v>-235800</v>
       </c>
       <c r="E32" s="3">
-        <v>-102000</v>
+        <v>-413500</v>
       </c>
       <c r="F32" s="3">
-        <v>-166300</v>
+        <v>-104600</v>
       </c>
       <c r="G32" s="3">
-        <v>16600</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
+        <v>-170600</v>
+      </c>
+      <c r="H32" s="3">
+        <v>17100</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
@@ -1332,26 +1401,29 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-157400</v>
+        <v>2244500</v>
       </c>
       <c r="E33" s="3">
-        <v>3879000</v>
+        <v>-161400</v>
       </c>
       <c r="F33" s="3">
-        <v>2951900</v>
+        <v>3977800</v>
       </c>
       <c r="G33" s="3">
-        <v>-75500</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
+        <v>3027100</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-77400</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>3</v>
@@ -1359,9 +1431,12 @@
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1386,26 +1461,29 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-157400</v>
+        <v>2244500</v>
       </c>
       <c r="E35" s="3">
-        <v>3879000</v>
+        <v>-161400</v>
       </c>
       <c r="F35" s="3">
-        <v>2951900</v>
+        <v>3977800</v>
       </c>
       <c r="G35" s="3">
-        <v>-75500</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
+        <v>3027100</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-77400</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>3</v>
@@ -1413,41 +1491,47 @@
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L35" s="3"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45016</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44651</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44286</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43921</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1459,8 +1543,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1472,25 +1557,26 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1141200</v>
+        <v>1359300</v>
       </c>
       <c r="E41" s="3">
-        <v>1342700</v>
+        <v>1170200</v>
       </c>
       <c r="F41" s="3">
-        <v>2047600</v>
+        <v>1376900</v>
       </c>
       <c r="G41" s="3">
-        <v>210600</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
+        <v>2099800</v>
+      </c>
+      <c r="H41" s="3">
+        <v>216000</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
@@ -1498,9 +1584,12 @@
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1525,26 +1614,29 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>7116000</v>
+        <v>2738400</v>
       </c>
       <c r="E43" s="3">
-        <v>2617100</v>
+        <v>7297300</v>
       </c>
       <c r="F43" s="3">
-        <v>1676500</v>
+        <v>2683700</v>
       </c>
       <c r="G43" s="3">
-        <v>1795700</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
+        <v>1719200</v>
+      </c>
+      <c r="H43" s="3">
+        <v>1841400</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
@@ -1552,26 +1644,29 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1010600</v>
+        <v>450100</v>
       </c>
       <c r="E44" s="3">
-        <v>341100</v>
+        <v>1036400</v>
       </c>
       <c r="F44" s="3">
-        <v>300600</v>
+        <v>349800</v>
       </c>
       <c r="G44" s="3">
-        <v>222700</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
+        <v>308200</v>
+      </c>
+      <c r="H44" s="3">
+        <v>228300</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
@@ -1579,26 +1674,29 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2767900</v>
+        <v>2484100</v>
       </c>
       <c r="E45" s="3">
-        <v>4575500</v>
+        <v>2838400</v>
       </c>
       <c r="F45" s="3">
-        <v>1760200</v>
+        <v>4692000</v>
       </c>
       <c r="G45" s="3">
-        <v>2219100</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
+        <v>1805100</v>
+      </c>
+      <c r="H45" s="3">
+        <v>2275600</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
@@ -1606,26 +1704,29 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>7378000</v>
+        <v>7031900</v>
       </c>
       <c r="E46" s="3">
-        <v>8876400</v>
+        <v>7565900</v>
       </c>
       <c r="F46" s="3">
-        <v>5785000</v>
+        <v>9102500</v>
       </c>
       <c r="G46" s="3">
-        <v>4448100</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
+        <v>5932300</v>
+      </c>
+      <c r="H46" s="3">
+        <v>4561300</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
@@ -1633,26 +1734,29 @@
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L46" s="3"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>4175200</v>
+        <v>4578800</v>
       </c>
       <c r="E47" s="3">
-        <v>2714700</v>
+        <v>4288300</v>
       </c>
       <c r="F47" s="3">
-        <v>2965200</v>
+        <v>2783800</v>
       </c>
       <c r="G47" s="3">
-        <v>3579200</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
+        <v>3040800</v>
+      </c>
+      <c r="H47" s="3">
+        <v>3670400</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
@@ -1660,26 +1764,29 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>39401500</v>
+        <v>21797600</v>
       </c>
       <c r="E48" s="3">
-        <v>18706200</v>
+        <v>40405000</v>
       </c>
       <c r="F48" s="3">
-        <v>16960300</v>
+        <v>19182700</v>
       </c>
       <c r="G48" s="3">
-        <v>16397800</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
+        <v>17392300</v>
+      </c>
+      <c r="H48" s="3">
+        <v>16815400</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
@@ -1687,26 +1794,29 @@
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5016800</v>
+        <v>3050300</v>
       </c>
       <c r="E49" s="3">
-        <v>1443100</v>
+        <v>5144600</v>
       </c>
       <c r="F49" s="3">
-        <v>1076500</v>
+        <v>1479900</v>
       </c>
       <c r="G49" s="3">
-        <v>1409400</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
+        <v>1104000</v>
+      </c>
+      <c r="H49" s="3">
+        <v>1445300</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>3</v>
@@ -1714,9 +1824,12 @@
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1741,9 +1854,12 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1768,26 +1884,29 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3"/>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1007200</v>
+        <v>637500</v>
       </c>
       <c r="E52" s="3">
-        <v>1224100</v>
+        <v>1032800</v>
       </c>
       <c r="F52" s="3">
-        <v>841700</v>
+        <v>1255300</v>
       </c>
       <c r="G52" s="3">
-        <v>1077900</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
+        <v>863200</v>
+      </c>
+      <c r="H52" s="3">
+        <v>1105400</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
@@ -1795,9 +1914,12 @@
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1822,26 +1944,29 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3"/>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>34769600</v>
+        <v>37096200</v>
       </c>
       <c r="E54" s="3">
-        <v>32964500</v>
+        <v>35661800</v>
       </c>
       <c r="F54" s="3">
-        <v>27628800</v>
+        <v>33804100</v>
       </c>
       <c r="G54" s="3">
-        <v>26912400</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
+        <v>28332500</v>
+      </c>
+      <c r="H54" s="3">
+        <v>27597800</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
@@ -1849,9 +1974,12 @@
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1863,8 +1991,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1876,25 +2005,26 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4290800</v>
+        <v>861700</v>
       </c>
       <c r="E57" s="3">
-        <v>1176900</v>
+        <v>4400100</v>
       </c>
       <c r="F57" s="3">
-        <v>554500</v>
+        <v>1206800</v>
       </c>
       <c r="G57" s="3">
-        <v>528700</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
+        <v>568600</v>
+      </c>
+      <c r="H57" s="3">
+        <v>542200</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
@@ -1902,26 +2032,29 @@
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2329700</v>
+        <v>1480200</v>
       </c>
       <c r="E58" s="3">
-        <v>1523800</v>
+        <v>2389000</v>
       </c>
       <c r="F58" s="3">
-        <v>1199800</v>
+        <v>1562600</v>
       </c>
       <c r="G58" s="3">
-        <v>2516900</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
+        <v>1230300</v>
+      </c>
+      <c r="H58" s="3">
+        <v>2581000</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
@@ -1929,26 +2062,29 @@
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L58" s="3"/>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2878900</v>
+        <v>4036500</v>
       </c>
       <c r="E59" s="3">
-        <v>3260100</v>
+        <v>3973200</v>
       </c>
       <c r="F59" s="3">
-        <v>2736200</v>
+        <v>3343100</v>
       </c>
       <c r="G59" s="3">
-        <v>3618900</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
+        <v>2805900</v>
+      </c>
+      <c r="H59" s="3">
+        <v>3711000</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
@@ -1956,26 +2092,29 @@
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3"/>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>6097300</v>
+        <v>6378300</v>
       </c>
       <c r="E60" s="3">
-        <v>5960700</v>
+        <v>7273700</v>
       </c>
       <c r="F60" s="3">
-        <v>4490400</v>
+        <v>6112500</v>
       </c>
       <c r="G60" s="3">
-        <v>6664500</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
+        <v>4604800</v>
+      </c>
+      <c r="H60" s="3">
+        <v>6834200</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
@@ -1983,26 +2122,29 @@
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K60" s="3"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L60" s="3"/>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>9263500</v>
+        <v>10505100</v>
       </c>
       <c r="E61" s="3">
-        <v>10075500</v>
+        <v>9499400</v>
       </c>
       <c r="F61" s="3">
-        <v>10842100</v>
+        <v>10332100</v>
       </c>
       <c r="G61" s="3">
-        <v>10499800</v>
+        <v>11118300</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>10767300</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2010,26 +2152,29 @@
       <c r="J61" s="3">
         <v>0</v>
       </c>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3"/>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>6450600</v>
+        <v>4724700</v>
       </c>
       <c r="E62" s="3">
-        <v>5189500</v>
+        <v>5604900</v>
       </c>
       <c r="F62" s="3">
-        <v>3747100</v>
+        <v>5321600</v>
       </c>
       <c r="G62" s="3">
-        <v>3452300</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
+        <v>3842500</v>
+      </c>
+      <c r="H62" s="3">
+        <v>3540200</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
@@ -2037,9 +2182,12 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2064,9 +2212,12 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3"/>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2091,9 +2242,12 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2118,26 +2272,29 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>21413800</v>
+        <v>22592100</v>
       </c>
       <c r="E66" s="3">
-        <v>21277600</v>
+        <v>21970200</v>
       </c>
       <c r="F66" s="3">
-        <v>19079600</v>
+        <v>21819500</v>
       </c>
       <c r="G66" s="3">
-        <v>20616600</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
+        <v>19565600</v>
+      </c>
+      <c r="H66" s="3">
+        <v>21141600</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
@@ -2145,9 +2302,12 @@
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L66" s="3"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2159,8 +2319,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2185,9 +2346,12 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2212,9 +2376,12 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2239,9 +2406,12 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2266,26 +2436,29 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3"/>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>8590700</v>
+        <v>9707100</v>
       </c>
       <c r="E72" s="3">
-        <v>8479300</v>
+        <v>8805100</v>
       </c>
       <c r="F72" s="3">
-        <v>5080400</v>
+        <v>8695300</v>
       </c>
       <c r="G72" s="3">
-        <v>3143200</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
+        <v>5209800</v>
+      </c>
+      <c r="H72" s="3">
+        <v>3223300</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
@@ -2293,9 +2466,12 @@
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L72" s="3"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2320,9 +2496,12 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3"/>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2347,9 +2526,12 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2374,26 +2556,29 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>13355800</v>
+        <v>14504000</v>
       </c>
       <c r="E76" s="3">
-        <v>11686900</v>
+        <v>13691600</v>
       </c>
       <c r="F76" s="3">
-        <v>8549200</v>
+        <v>11984600</v>
       </c>
       <c r="G76" s="3">
-        <v>6295800</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
+        <v>8766900</v>
+      </c>
+      <c r="H76" s="3">
+        <v>6456200</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
@@ -2401,9 +2586,12 @@
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K76" s="3"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2428,58 +2616,64 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45016</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44651</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44286</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43921</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-157400</v>
+        <v>2244500</v>
       </c>
       <c r="E81" s="3">
-        <v>3879000</v>
+        <v>-161400</v>
       </c>
       <c r="F81" s="3">
-        <v>2951900</v>
+        <v>3977800</v>
       </c>
       <c r="G81" s="3">
-        <v>-75500</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
+        <v>3027100</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-77400</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>3</v>
@@ -2487,9 +2681,12 @@
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L81" s="3"/>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2501,22 +2698,23 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>819800</v>
+        <v>1127200</v>
       </c>
       <c r="E83" s="3">
-        <v>388000</v>
+        <v>840700</v>
       </c>
       <c r="F83" s="3">
-        <v>816300</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
+        <v>397900</v>
+      </c>
+      <c r="G83" s="3">
+        <v>837100</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
@@ -2527,9 +2725,12 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3"/>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2554,9 +2755,12 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3"/>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2581,9 +2785,12 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3"/>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2608,9 +2815,12 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3"/>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2635,9 +2845,12 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3"/>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2662,23 +2875,26 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3"/>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1911700</v>
+        <v>5065100</v>
       </c>
       <c r="E89" s="3">
-        <v>2083100</v>
+        <v>1960400</v>
       </c>
       <c r="F89" s="3">
-        <v>2325300</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
+        <v>2136100</v>
+      </c>
+      <c r="G89" s="3">
+        <v>2384500</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>3</v>
@@ -2689,9 +2905,12 @@
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3"/>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2703,22 +2922,23 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1893400</v>
+        <v>-2585400</v>
       </c>
       <c r="E91" s="3">
-        <v>-1629700</v>
+        <v>-1941700</v>
       </c>
       <c r="F91" s="3">
-        <v>-1260400</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
+        <v>-1671200</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-1292500</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>3</v>
@@ -2729,9 +2949,12 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3"/>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2756,9 +2979,12 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2783,23 +3009,26 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3"/>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-3793300</v>
+        <v>-3750700</v>
       </c>
       <c r="E94" s="3">
-        <v>-953200</v>
+        <v>-3889900</v>
       </c>
       <c r="F94" s="3">
-        <v>567800</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
+        <v>-977500</v>
+      </c>
+      <c r="G94" s="3">
+        <v>582200</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
@@ -2810,9 +3039,12 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3"/>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2824,22 +3056,23 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-606900</v>
+        <v>-1204300</v>
       </c>
       <c r="E96" s="3">
-        <v>-648300</v>
+        <v>-622400</v>
       </c>
       <c r="F96" s="3">
-        <v>-1020400</v>
+        <v>-664800</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>-1046300</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
@@ -2850,9 +3083,12 @@
       <c r="J96" s="3">
         <v>0</v>
       </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3"/>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -2877,9 +3113,12 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3"/>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -2904,9 +3143,12 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3"/>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3"/>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -2931,23 +3173,26 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3"/>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3"/>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1680000</v>
+        <v>-1125300</v>
       </c>
       <c r="E100" s="3">
-        <v>-1834800</v>
+        <v>1722800</v>
       </c>
       <c r="F100" s="3">
-        <v>-1056100</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
+        <v>-1881600</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-1083000</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
@@ -2958,9 +3203,12 @@
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -2985,23 +3233,26 @@
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3"/>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-201500</v>
+        <v>189100</v>
       </c>
       <c r="E102" s="3">
-        <v>-704900</v>
+        <v>-206700</v>
       </c>
       <c r="F102" s="3">
-        <v>1837000</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
+        <v>-722900</v>
+      </c>
+      <c r="G102" s="3">
+        <v>1883800</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>3</v>
@@ -3012,7 +3263,10 @@
       <c r="J102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K102" s="3"/>
+      <c r="K102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SSEZY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSEZY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
   <si>
     <t>SSEZY</t>
   </si>
@@ -662,8 +662,8 @@
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -696,11 +696,11 @@
       <c r="H7" s="2">
         <v>43921</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
+      <c r="I7" s="2">
+        <v>43555</v>
+      </c>
+      <c r="J7" s="2">
+        <v>43190</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
@@ -712,25 +712,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>13721900</v>
+        <v>13207200</v>
       </c>
       <c r="E8" s="3">
-        <v>16390300</v>
+        <v>15452700</v>
       </c>
       <c r="F8" s="3">
-        <v>11295700</v>
+        <v>11432600</v>
       </c>
       <c r="G8" s="3">
-        <v>8957600</v>
+        <v>9404300</v>
       </c>
       <c r="H8" s="3">
-        <v>8923700</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
+        <v>8466800</v>
+      </c>
+      <c r="I8" s="3">
+        <v>9508500</v>
+      </c>
+      <c r="J8" s="3">
+        <v>38248900</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -742,25 +742,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>8013600</v>
+        <v>7713000</v>
       </c>
       <c r="E9" s="3">
-        <v>16599900</v>
+        <v>15650200</v>
       </c>
       <c r="F9" s="3">
-        <v>5528300</v>
+        <v>5662500</v>
       </c>
       <c r="G9" s="3">
-        <v>5424800</v>
+        <v>5695300</v>
       </c>
       <c r="H9" s="3">
-        <v>6278000</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+        <v>5956500</v>
+      </c>
+      <c r="I9" s="3">
+        <v>7697300</v>
+      </c>
+      <c r="J9" s="3">
+        <v>35053100</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -772,25 +772,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>5708300</v>
+        <v>5494200</v>
       </c>
       <c r="E10" s="3">
-        <v>-209600</v>
+        <v>-197600</v>
       </c>
       <c r="F10" s="3">
-        <v>5767400</v>
+        <v>5770000</v>
       </c>
       <c r="G10" s="3">
-        <v>3532800</v>
+        <v>3709000</v>
       </c>
       <c r="H10" s="3">
-        <v>2645800</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+        <v>2510300</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1811200</v>
+      </c>
+      <c r="J10" s="3">
+        <v>3195700</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -815,26 +815,26 @@
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
+      <c r="D12" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>13400</v>
+      </c>
+      <c r="F12" s="3">
+        <v>15800</v>
+      </c>
+      <c r="G12" s="3">
+        <v>16500</v>
+      </c>
+      <c r="H12" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I12" s="3">
+        <v>4800</v>
+      </c>
+      <c r="J12" s="3">
+        <v>8000</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
@@ -876,25 +876,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>518100</v>
+        <v>336000</v>
       </c>
       <c r="E14" s="3">
-        <v>304600</v>
+        <v>174600</v>
       </c>
       <c r="F14" s="3">
-        <v>-400200</v>
+        <v>-395300</v>
       </c>
       <c r="G14" s="3">
-        <v>-1076300</v>
+        <v>-1173300</v>
       </c>
       <c r="H14" s="3">
-        <v>276000</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+        <v>261100</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-1316700</v>
+      </c>
+      <c r="J14" s="3">
+        <v>219500</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -906,25 +906,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>734500</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>678400</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>657300</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>652600</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>628200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>675500</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>1086100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -947,25 +947,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>10299100</v>
+        <v>9525100</v>
       </c>
       <c r="E17" s="3">
-        <v>16582000</v>
+        <v>16145600</v>
       </c>
       <c r="F17" s="3">
-        <v>6363600</v>
+        <v>7027800</v>
       </c>
       <c r="G17" s="3">
-        <v>5472000</v>
+        <v>6966600</v>
       </c>
       <c r="H17" s="3">
-        <v>7656400</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
+        <v>7186700</v>
+      </c>
+      <c r="I17" s="3">
+        <v>8879800</v>
+      </c>
+      <c r="J17" s="3">
+        <v>36606200</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -977,25 +977,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3422900</v>
+        <v>3682100</v>
       </c>
       <c r="E18" s="3">
-        <v>-191700</v>
+        <v>-692900</v>
       </c>
       <c r="F18" s="3">
-        <v>4932000</v>
+        <v>4404800</v>
       </c>
       <c r="G18" s="3">
-        <v>3485600</v>
+        <v>2437700</v>
       </c>
       <c r="H18" s="3">
-        <v>1267300</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+        <v>1280100</v>
+      </c>
+      <c r="I18" s="3">
+        <v>628700</v>
+      </c>
+      <c r="J18" s="3">
+        <v>1642600</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1021,25 +1021,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>235800</v>
+        <v>10900</v>
       </c>
       <c r="E20" s="3">
-        <v>413500</v>
+        <v>-956600</v>
       </c>
       <c r="F20" s="3">
-        <v>104600</v>
+        <v>-147100</v>
       </c>
       <c r="G20" s="3">
-        <v>170600</v>
+        <v>-124700</v>
       </c>
       <c r="H20" s="3">
-        <v>-17100</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+        <v>-89400</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-109900</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-149800</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1051,25 +1051,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4785900</v>
+        <v>4405800</v>
       </c>
       <c r="E21" s="3">
-        <v>1062600</v>
+        <v>942100</v>
       </c>
       <c r="F21" s="3">
-        <v>5434500</v>
+        <v>5209100</v>
       </c>
       <c r="G21" s="3">
-        <v>4493300</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>3215000</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1997700</v>
+      </c>
+      <c r="I21" s="3">
+        <v>1414100</v>
+      </c>
+      <c r="J21" s="3">
+        <v>2878500</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1081,25 +1081,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>384600</v>
+        <v>402000</v>
       </c>
       <c r="E22" s="3">
-        <v>491600</v>
+        <v>490800</v>
       </c>
       <c r="F22" s="3">
-        <v>467300</v>
+        <v>475600</v>
       </c>
       <c r="G22" s="3">
-        <v>483300</v>
+        <v>512600</v>
       </c>
       <c r="H22" s="3">
-        <v>479200</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+        <v>466100</v>
+      </c>
+      <c r="I22" s="3">
+        <v>463000</v>
+      </c>
+      <c r="J22" s="3">
+        <v>499100</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1111,25 +1111,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>3274100</v>
+        <v>3151300</v>
       </c>
       <c r="E23" s="3">
-        <v>-269800</v>
+        <v>-254400</v>
       </c>
       <c r="F23" s="3">
-        <v>4569300</v>
+        <v>4569600</v>
       </c>
       <c r="G23" s="3">
-        <v>3172900</v>
+        <v>3331100</v>
       </c>
       <c r="H23" s="3">
-        <v>771000</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
+        <v>731600</v>
+      </c>
+      <c r="I23" s="3">
+        <v>1693300</v>
+      </c>
+      <c r="J23" s="3">
+        <v>1213300</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1141,25 +1141,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>801400</v>
+        <v>771300</v>
       </c>
       <c r="E24" s="3">
-        <v>-144300</v>
+        <v>-136100</v>
       </c>
       <c r="F24" s="3">
-        <v>1158400</v>
+        <v>1158500</v>
       </c>
       <c r="G24" s="3">
-        <v>294300</v>
+        <v>309000</v>
       </c>
       <c r="H24" s="3">
-        <v>159400</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+        <v>151300</v>
+      </c>
+      <c r="I24" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="J24" s="3">
+        <v>163400</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1201,25 +1201,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>2472700</v>
+        <v>2380000</v>
       </c>
       <c r="E26" s="3">
-        <v>-125400</v>
+        <v>-118300</v>
       </c>
       <c r="F26" s="3">
-        <v>3410900</v>
+        <v>3411200</v>
       </c>
       <c r="G26" s="3">
-        <v>2878600</v>
+        <v>3022100</v>
       </c>
       <c r="H26" s="3">
-        <v>611600</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
+        <v>580300</v>
+      </c>
+      <c r="I26" s="3">
+        <v>1706200</v>
+      </c>
+      <c r="J26" s="3">
+        <v>1049900</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1231,25 +1231,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>2244500</v>
+        <v>2160300</v>
       </c>
       <c r="E27" s="3">
-        <v>-207300</v>
+        <v>-152200</v>
       </c>
       <c r="F27" s="3">
-        <v>3344400</v>
+        <v>3979000</v>
       </c>
       <c r="G27" s="3">
-        <v>2817400</v>
+        <v>3135800</v>
       </c>
       <c r="H27" s="3">
-        <v>550600</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
+        <v>-73500</v>
+      </c>
+      <c r="I27" s="3">
+        <v>1835000</v>
+      </c>
+      <c r="J27" s="3">
+        <v>1153200</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1294,22 +1294,22 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>45900</v>
+        <v>43300</v>
       </c>
       <c r="F29" s="3">
-        <v>633400</v>
+        <v>634500</v>
       </c>
       <c r="G29" s="3">
-        <v>209700</v>
+        <v>177900</v>
       </c>
       <c r="H29" s="3">
-        <v>-628000</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>3</v>
+        <v>-595900</v>
+      </c>
+      <c r="I29" s="3">
+        <v>189500</v>
+      </c>
+      <c r="J29" s="3">
+        <v>241600</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>3</v>
@@ -1381,25 +1381,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-235800</v>
+        <v>-10900</v>
       </c>
       <c r="E32" s="3">
-        <v>-413500</v>
+        <v>956600</v>
       </c>
       <c r="F32" s="3">
-        <v>-104600</v>
+        <v>147100</v>
       </c>
       <c r="G32" s="3">
-        <v>-170600</v>
+        <v>124700</v>
       </c>
       <c r="H32" s="3">
-        <v>17100</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+        <v>89400</v>
+      </c>
+      <c r="I32" s="3">
+        <v>109900</v>
+      </c>
+      <c r="J32" s="3">
+        <v>149800</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1411,25 +1411,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2244500</v>
+        <v>2160300</v>
       </c>
       <c r="E33" s="3">
-        <v>-161400</v>
+        <v>-152200</v>
       </c>
       <c r="F33" s="3">
-        <v>3977800</v>
+        <v>3979000</v>
       </c>
       <c r="G33" s="3">
-        <v>3027100</v>
+        <v>3135800</v>
       </c>
       <c r="H33" s="3">
-        <v>-77400</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
+        <v>-73500</v>
+      </c>
+      <c r="I33" s="3">
+        <v>1895700</v>
+      </c>
+      <c r="J33" s="3">
+        <v>1291500</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1471,25 +1471,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2244500</v>
+        <v>2160300</v>
       </c>
       <c r="E35" s="3">
-        <v>-161400</v>
+        <v>-152200</v>
       </c>
       <c r="F35" s="3">
-        <v>3977800</v>
+        <v>3979000</v>
       </c>
       <c r="G35" s="3">
-        <v>3027100</v>
+        <v>3135800</v>
       </c>
       <c r="H35" s="3">
-        <v>-77400</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
+        <v>-73500</v>
+      </c>
+      <c r="I35" s="3">
+        <v>1895700</v>
+      </c>
+      <c r="J35" s="3">
+        <v>1291500</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1520,11 +1520,11 @@
       <c r="H38" s="2">
         <v>43921</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
+      <c r="I38" s="2">
+        <v>43555</v>
+      </c>
+      <c r="J38" s="2">
+        <v>43190</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
@@ -1564,25 +1564,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1359300</v>
+        <v>1308300</v>
       </c>
       <c r="E41" s="3">
-        <v>1170200</v>
+        <v>1103300</v>
       </c>
       <c r="F41" s="3">
-        <v>1376900</v>
+        <v>1379300</v>
       </c>
       <c r="G41" s="3">
-        <v>2099800</v>
+        <v>2204500</v>
       </c>
       <c r="H41" s="3">
-        <v>216000</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+        <v>204900</v>
+      </c>
+      <c r="I41" s="3">
+        <v>562100</v>
+      </c>
+      <c r="J41" s="3">
+        <v>325900</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1600,19 +1600,19 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>4900</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -1624,25 +1624,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2738400</v>
+        <v>2635700</v>
       </c>
       <c r="E43" s="3">
-        <v>7297300</v>
+        <v>2865200</v>
       </c>
       <c r="F43" s="3">
-        <v>2683700</v>
+        <v>2682000</v>
       </c>
       <c r="G43" s="3">
-        <v>1719200</v>
+        <v>1799700</v>
       </c>
       <c r="H43" s="3">
-        <v>1841400</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+        <v>1739300</v>
+      </c>
+      <c r="I43" s="3">
+        <v>1871000</v>
+      </c>
+      <c r="J43" s="3">
+        <v>5473400</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -1654,25 +1654,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>450100</v>
+        <v>433200</v>
       </c>
       <c r="E44" s="3">
-        <v>1036400</v>
+        <v>488500</v>
       </c>
       <c r="F44" s="3">
-        <v>349800</v>
+        <v>350400</v>
       </c>
       <c r="G44" s="3">
-        <v>308200</v>
+        <v>323600</v>
       </c>
       <c r="H44" s="3">
-        <v>228300</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
+        <v>216600</v>
+      </c>
+      <c r="I44" s="3">
+        <v>297600</v>
+      </c>
+      <c r="J44" s="3">
+        <v>317100</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
@@ -1684,25 +1684,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2484100</v>
+        <v>1645300</v>
       </c>
       <c r="E45" s="3">
-        <v>2838400</v>
+        <v>1931700</v>
       </c>
       <c r="F45" s="3">
-        <v>4692000</v>
+        <v>4470800</v>
       </c>
       <c r="G45" s="3">
-        <v>1805100</v>
+        <v>1632400</v>
       </c>
       <c r="H45" s="3">
-        <v>2275600</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+        <v>1694700</v>
+      </c>
+      <c r="I45" s="3">
+        <v>3862300</v>
+      </c>
+      <c r="J45" s="3">
+        <v>2652500</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -1714,25 +1714,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>7031900</v>
+        <v>6768200</v>
       </c>
       <c r="E46" s="3">
-        <v>7565900</v>
+        <v>7133100</v>
       </c>
       <c r="F46" s="3">
-        <v>9102500</v>
+        <v>9118500</v>
       </c>
       <c r="G46" s="3">
-        <v>5932300</v>
+        <v>6228200</v>
       </c>
       <c r="H46" s="3">
-        <v>4561300</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
+        <v>4327800</v>
+      </c>
+      <c r="I46" s="3">
+        <v>7114000</v>
+      </c>
+      <c r="J46" s="3">
+        <v>9010600</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -1744,25 +1744,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>4578800</v>
+        <v>2483500</v>
       </c>
       <c r="E47" s="3">
-        <v>4288300</v>
+        <v>2478100</v>
       </c>
       <c r="F47" s="3">
-        <v>2783800</v>
+        <v>1640800</v>
       </c>
       <c r="G47" s="3">
-        <v>3040800</v>
+        <v>2269100</v>
       </c>
       <c r="H47" s="3">
-        <v>3670400</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
+        <v>2302800</v>
+      </c>
+      <c r="I47" s="3">
+        <v>2473700</v>
+      </c>
+      <c r="J47" s="3">
+        <v>1378100</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -1774,25 +1774,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>21797600</v>
+        <v>20979900</v>
       </c>
       <c r="E48" s="3">
-        <v>40405000</v>
+        <v>19046800</v>
       </c>
       <c r="F48" s="3">
-        <v>19182700</v>
+        <v>19208700</v>
       </c>
       <c r="G48" s="3">
-        <v>17392300</v>
+        <v>18259600</v>
       </c>
       <c r="H48" s="3">
-        <v>16815400</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+        <v>15954400</v>
+      </c>
+      <c r="I48" s="3">
+        <v>16186400</v>
+      </c>
+      <c r="J48" s="3">
+        <v>17325100</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -1804,25 +1804,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>3050300</v>
+        <v>1901300</v>
       </c>
       <c r="E49" s="3">
-        <v>5144600</v>
+        <v>1776800</v>
       </c>
       <c r="F49" s="3">
-        <v>1479900</v>
+        <v>1218200</v>
       </c>
       <c r="G49" s="3">
-        <v>1104000</v>
+        <v>959100</v>
       </c>
       <c r="H49" s="3">
-        <v>1445300</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+        <v>840000</v>
+      </c>
+      <c r="I49" s="3">
+        <v>854500</v>
+      </c>
+      <c r="J49" s="3">
+        <v>1918300</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -1894,25 +1894,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>637500</v>
+        <v>613600</v>
       </c>
       <c r="E52" s="3">
-        <v>1032800</v>
+        <v>973700</v>
       </c>
       <c r="F52" s="3">
-        <v>1255300</v>
+        <v>1257500</v>
       </c>
       <c r="G52" s="3">
-        <v>863200</v>
+        <v>906200</v>
       </c>
       <c r="H52" s="3">
-        <v>1105400</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+        <v>1048800</v>
+      </c>
+      <c r="I52" s="3">
+        <v>1018500</v>
+      </c>
+      <c r="J52" s="3">
+        <v>1275200</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -1954,25 +1954,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>37096200</v>
+        <v>35704600</v>
       </c>
       <c r="E54" s="3">
-        <v>35661800</v>
+        <v>33621700</v>
       </c>
       <c r="F54" s="3">
-        <v>33804100</v>
+        <v>33855900</v>
       </c>
       <c r="G54" s="3">
-        <v>28332500</v>
+        <v>29745400</v>
       </c>
       <c r="H54" s="3">
-        <v>27597800</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+        <v>26184600</v>
+      </c>
+      <c r="I54" s="3">
+        <v>29261100</v>
+      </c>
+      <c r="J54" s="3">
+        <v>32584700</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2012,25 +2012,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>861700</v>
+        <v>829400</v>
       </c>
       <c r="E57" s="3">
-        <v>4400100</v>
+        <v>859300</v>
       </c>
       <c r="F57" s="3">
-        <v>1206800</v>
+        <v>1209000</v>
       </c>
       <c r="G57" s="3">
-        <v>568600</v>
+        <v>596900</v>
       </c>
       <c r="H57" s="3">
-        <v>542200</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+        <v>514400</v>
+      </c>
+      <c r="I57" s="3">
+        <v>1460000</v>
+      </c>
+      <c r="J57" s="3">
+        <v>3596900</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2042,25 +2042,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1480200</v>
+        <v>1464200</v>
       </c>
       <c r="E58" s="3">
-        <v>2389000</v>
+        <v>2269000</v>
       </c>
       <c r="F58" s="3">
-        <v>1562600</v>
+        <v>1659200</v>
       </c>
       <c r="G58" s="3">
-        <v>1230300</v>
+        <v>1431400</v>
       </c>
       <c r="H58" s="3">
-        <v>2581000</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>2521600</v>
+      </c>
+      <c r="I58" s="3">
+        <v>990000</v>
+      </c>
+      <c r="J58" s="3">
+        <v>1025800</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2072,25 +2072,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4036500</v>
+        <v>1653700</v>
       </c>
       <c r="E59" s="3">
-        <v>3973200</v>
+        <v>2057400</v>
       </c>
       <c r="F59" s="3">
-        <v>3343100</v>
+        <v>1445800</v>
       </c>
       <c r="G59" s="3">
-        <v>2805900</v>
+        <v>1090400</v>
       </c>
       <c r="H59" s="3">
-        <v>3711000</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+        <v>1861000</v>
+      </c>
+      <c r="I59" s="3">
+        <v>2840100</v>
+      </c>
+      <c r="J59" s="3">
+        <v>3483800</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2102,25 +2102,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>6378300</v>
+        <v>6139100</v>
       </c>
       <c r="E60" s="3">
-        <v>7273700</v>
+        <v>6857600</v>
       </c>
       <c r="F60" s="3">
-        <v>6112500</v>
+        <v>6123200</v>
       </c>
       <c r="G60" s="3">
-        <v>4604800</v>
+        <v>4834400</v>
       </c>
       <c r="H60" s="3">
-        <v>6834200</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
+        <v>6484200</v>
+      </c>
+      <c r="I60" s="3">
+        <v>6915800</v>
+      </c>
+      <c r="J60" s="3">
+        <v>9852600</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2132,25 +2132,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>10505100</v>
+        <v>10192500</v>
       </c>
       <c r="E61" s="3">
-        <v>9499400</v>
+        <v>9053800</v>
       </c>
       <c r="F61" s="3">
-        <v>10332100</v>
+        <v>10749700</v>
       </c>
       <c r="G61" s="3">
-        <v>11118300</v>
+        <v>12237700</v>
       </c>
       <c r="H61" s="3">
-        <v>10767300</v>
+        <v>10827900</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>11811200</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>11733700</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2162,25 +2162,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4724700</v>
+        <v>1144900</v>
       </c>
       <c r="E62" s="3">
-        <v>5604900</v>
+        <v>1204200</v>
       </c>
       <c r="F62" s="3">
-        <v>5321600</v>
+        <v>2508200</v>
       </c>
       <c r="G62" s="3">
-        <v>3842500</v>
+        <v>1865500</v>
       </c>
       <c r="H62" s="3">
-        <v>3540200</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+        <v>1442800</v>
+      </c>
+      <c r="I62" s="3">
+        <v>1595300</v>
+      </c>
+      <c r="J62" s="3">
+        <v>1668300</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2282,25 +2282,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>22592100</v>
+        <v>20797600</v>
       </c>
       <c r="E66" s="3">
-        <v>21970200</v>
+        <v>19910300</v>
       </c>
       <c r="F66" s="3">
-        <v>21819500</v>
+        <v>21802600</v>
       </c>
       <c r="G66" s="3">
-        <v>19565600</v>
+        <v>20541300</v>
       </c>
       <c r="H66" s="3">
-        <v>21141600</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+        <v>20059000</v>
+      </c>
+      <c r="I66" s="3">
+        <v>21718000</v>
+      </c>
+      <c r="J66" s="3">
+        <v>25243600</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2446,25 +2446,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>9707100</v>
+        <v>9276600</v>
       </c>
       <c r="E72" s="3">
-        <v>8805100</v>
+        <v>8236300</v>
       </c>
       <c r="F72" s="3">
-        <v>8695300</v>
+        <v>8640100</v>
       </c>
       <c r="G72" s="3">
-        <v>5209800</v>
+        <v>5401900</v>
       </c>
       <c r="H72" s="3">
-        <v>3223300</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+        <v>2997000</v>
+      </c>
+      <c r="I72" s="3">
+        <v>4281900</v>
+      </c>
+      <c r="J72" s="3">
+        <v>3643900</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -2566,25 +2566,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>14504000</v>
+        <v>13959900</v>
       </c>
       <c r="E76" s="3">
-        <v>13691600</v>
+        <v>12908400</v>
       </c>
       <c r="F76" s="3">
-        <v>11984600</v>
+        <v>11999900</v>
       </c>
       <c r="G76" s="3">
-        <v>8766900</v>
+        <v>9204100</v>
       </c>
       <c r="H76" s="3">
-        <v>6456200</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+        <v>6125500</v>
+      </c>
+      <c r="I76" s="3">
+        <v>7543100</v>
+      </c>
+      <c r="J76" s="3">
+        <v>7341100</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -2645,11 +2645,11 @@
       <c r="H80" s="2">
         <v>43921</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
+      <c r="I80" s="2">
+        <v>43555</v>
+      </c>
+      <c r="J80" s="2">
+        <v>43190</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
@@ -2661,25 +2661,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2244500</v>
+        <v>2160300</v>
       </c>
       <c r="E81" s="3">
-        <v>-161400</v>
+        <v>-152200</v>
       </c>
       <c r="F81" s="3">
-        <v>3977800</v>
+        <v>3979000</v>
       </c>
       <c r="G81" s="3">
-        <v>3027100</v>
+        <v>3135800</v>
       </c>
       <c r="H81" s="3">
-        <v>-77400</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
+        <v>-73500</v>
+      </c>
+      <c r="I81" s="3">
+        <v>1895700</v>
+      </c>
+      <c r="J81" s="3">
+        <v>1291500</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -2705,25 +2705,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1127200</v>
+        <v>793900</v>
       </c>
       <c r="E83" s="3">
-        <v>840700</v>
+        <v>749300</v>
       </c>
       <c r="F83" s="3">
-        <v>397900</v>
+        <v>716800</v>
       </c>
       <c r="G83" s="3">
-        <v>837100</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+        <v>720900</v>
+      </c>
+      <c r="H83" s="3">
+        <v>626400</v>
+      </c>
+      <c r="I83" s="3">
+        <v>663900</v>
+      </c>
+      <c r="J83" s="3">
+        <v>1017300</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -2885,25 +2885,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>5065100</v>
+        <v>4875100</v>
       </c>
       <c r="E89" s="3">
-        <v>1960400</v>
+        <v>1848300</v>
       </c>
       <c r="F89" s="3">
-        <v>2136100</v>
+        <v>2139900</v>
       </c>
       <c r="G89" s="3">
-        <v>2384500</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+        <v>2503400</v>
+      </c>
+      <c r="H89" s="3">
+        <v>1618800</v>
+      </c>
+      <c r="I89" s="3">
+        <v>1532400</v>
+      </c>
+      <c r="J89" s="3">
+        <v>2424600</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -2929,25 +2929,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-2585400</v>
+        <v>-2488400</v>
       </c>
       <c r="E91" s="3">
-        <v>-1941700</v>
+        <v>-1830600</v>
       </c>
       <c r="F91" s="3">
-        <v>-1671200</v>
+        <v>-1674200</v>
       </c>
       <c r="G91" s="3">
-        <v>-1292500</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
+        <v>-1357000</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-1013600</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-1597100</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-1843800</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
@@ -3019,25 +3019,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-3750700</v>
+        <v>-3610000</v>
       </c>
       <c r="E94" s="3">
-        <v>-3889900</v>
+        <v>-3667400</v>
       </c>
       <c r="F94" s="3">
-        <v>-977500</v>
+        <v>-979200</v>
       </c>
       <c r="G94" s="3">
-        <v>582200</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+        <v>611300</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-1260200</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-940900</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-1974900</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3063,25 +3063,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1204300</v>
+        <v>1251500</v>
       </c>
       <c r="E96" s="3">
-        <v>-622400</v>
+        <v>634800</v>
       </c>
       <c r="F96" s="3">
-        <v>-664800</v>
+        <v>732600</v>
       </c>
       <c r="G96" s="3">
-        <v>-1046300</v>
+        <v>1162700</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>808600</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>959100</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>972700</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3183,25 +3183,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1125300</v>
+        <v>-1083100</v>
       </c>
       <c r="E100" s="3">
-        <v>1722800</v>
+        <v>1624200</v>
       </c>
       <c r="F100" s="3">
-        <v>-1881600</v>
+        <v>-1884900</v>
       </c>
       <c r="G100" s="3">
-        <v>-1083000</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+        <v>-1137000</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-809500</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-207800</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-2126700</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3212,26 +3212,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -3243,25 +3243,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>189100</v>
+        <v>182000</v>
       </c>
       <c r="E102" s="3">
-        <v>-206700</v>
+        <v>-194800</v>
       </c>
       <c r="F102" s="3">
-        <v>-722900</v>
+        <v>-724200</v>
       </c>
       <c r="G102" s="3">
-        <v>1883800</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+        <v>1977700</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-450900</v>
+      </c>
+      <c r="I102" s="3">
+        <v>383600</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-1677000</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/SSEZY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSEZY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
   <si>
     <t>SSEZY</t>
   </si>
@@ -656,148 +656,160 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44651</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44286</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43921</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43555</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43190</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>13090500</v>
+      </c>
+      <c r="E8" s="3">
         <v>13207200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>15452700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>11432600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9404300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8466800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9508500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>38248900</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>8098700</v>
+      </c>
+      <c r="E9" s="3">
         <v>7713000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>15650200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5662500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5695300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5956500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7697300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>35053100</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4991800</v>
+      </c>
+      <c r="E10" s="3">
         <v>5494200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-197600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5770000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3709000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2510300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1811200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3195700</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -810,38 +822,42 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E12" s="3">
         <v>16000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>13400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>15800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>16500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>4200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>4800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>8000</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -869,69 +885,78 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>399700</v>
+      </c>
+      <c r="E14" s="3">
         <v>336000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>174600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-395300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-1173300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>261100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1316700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>219500</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>775100</v>
+      </c>
+      <c r="E15" s="3">
         <v>734500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>678400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>657300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>652600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>628200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>675500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1086100</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -941,68 +966,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10183700</v>
+      </c>
+      <c r="E17" s="3">
         <v>9525100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>16145600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7027800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6966600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7186700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8879800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>36606200</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2906800</v>
+      </c>
+      <c r="E18" s="3">
         <v>3682100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-692900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4404800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2437700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1280100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>628700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1642600</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1015,158 +1047,174 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-71600</v>
+      </c>
+      <c r="E20" s="3">
         <v>10900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-956600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-147100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-124700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-89400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-109900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-149800</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3753400</v>
+      </c>
+      <c r="E21" s="3">
         <v>4405800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>942100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5209100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3215000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1997700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1414100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2878500</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>412200</v>
+      </c>
+      <c r="E22" s="3">
         <v>402000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>490800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>475600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>512600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>466100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>463000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>499100</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2391400</v>
+      </c>
+      <c r="E23" s="3">
         <v>3151300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-254400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4569600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3331100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>731600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1693300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1213300</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>669300</v>
+      </c>
+      <c r="E24" s="3">
         <v>771300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-136100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1158500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>309000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>151300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-12900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>163400</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1194,69 +1242,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1722100</v>
+      </c>
+      <c r="E26" s="3">
         <v>2380000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-118300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3411200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3022100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>580300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1706200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1049900</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1536700</v>
+      </c>
+      <c r="E27" s="3">
         <v>2160300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-152200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3979000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3135800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-73500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1835000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1153200</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1284,9 +1341,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1294,29 +1354,32 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>43300</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>634500</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>177900</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-595900</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>189500</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>241600</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1344,9 +1407,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1374,69 +1440,78 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>71600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-10900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>956600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>147100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>124700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>89400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>109900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>149800</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1536700</v>
+      </c>
+      <c r="E33" s="3">
         <v>2160300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-152200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3979000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3135800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-73500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1895700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1291500</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1464,74 +1539,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1536700</v>
+      </c>
+      <c r="E35" s="3">
         <v>2160300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-152200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3979000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3135800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-73500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1895700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1291500</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44651</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44286</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43921</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43555</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43190</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1544,8 +1628,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1558,38 +1643,42 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1408900</v>
+      </c>
+      <c r="E41" s="3">
         <v>1308300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1103300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1379300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2204500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>204900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>562100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>325900</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1600,236 +1689,260 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>6400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>7800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>7000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2696700</v>
+      </c>
+      <c r="E43" s="3">
         <v>2635700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2865200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2682000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1799700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1739300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1871000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5473400</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>598100</v>
+      </c>
+      <c r="E44" s="3">
         <v>433200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>488500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>350400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>323600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>216600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>297600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>317100</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1645300</v>
+        <v>737900</v>
       </c>
       <c r="E45" s="3">
+        <v>1630300</v>
+      </c>
+      <c r="F45" s="3">
         <v>1931700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4470800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1632400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1694700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3862300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2652500</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6585900</v>
+      </c>
+      <c r="E46" s="3">
         <v>6768200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7133100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9118500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6228200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4327800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7114000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9010600</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2579000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2483500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2478100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1640800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2269100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2302800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2473700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1378100</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>24320900</v>
+      </c>
+      <c r="E48" s="3">
         <v>20979900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>19046800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>19208700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>18259600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>15954400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>16186400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>17325100</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1719800</v>
+      </c>
+      <c r="E49" s="3">
         <v>1901300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1776800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1218200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>959100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>840000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>854500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1918300</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1857,9 +1970,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1887,39 +2003,45 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>738600</v>
+      </c>
+      <c r="E52" s="3">
         <v>613600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>973700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1257500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>906200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1048800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1018500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1275200</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1947,39 +2069,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>39230000</v>
+      </c>
+      <c r="E54" s="3">
         <v>35704600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>33621700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>33855900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>29745400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>26184600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>29261100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>32584700</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1992,8 +2120,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2006,188 +2135,207 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>918200</v>
+      </c>
+      <c r="E57" s="3">
         <v>829400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>859300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1209000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>596900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>514400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1460000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3596900</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2605800</v>
+      </c>
+      <c r="E58" s="3">
         <v>1464200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2269000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1659200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1431400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2521600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>990000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1025800</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1035900</v>
+      </c>
+      <c r="E59" s="3">
         <v>1653700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2057400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1445800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1090400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1861000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2840100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3483800</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6551900</v>
+      </c>
+      <c r="E60" s="3">
         <v>6139100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6857600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6123200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4834400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6484200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6915800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9852600</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11234400</v>
+      </c>
+      <c r="E61" s="3">
         <v>10192500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9053800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10749700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12237700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10827900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11811200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>11733700</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1049100</v>
+      </c>
+      <c r="E62" s="3">
         <v>1144900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1204200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2508200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1865500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1442800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1595300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1668300</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2215,9 +2363,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2245,9 +2396,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2275,39 +2429,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>22830800</v>
+      </c>
+      <c r="E66" s="3">
         <v>20797600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>19910300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>21802600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>20541300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>20059000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>21718000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>25243600</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2320,8 +2480,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2349,9 +2510,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2379,9 +2543,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2409,9 +2576,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2439,39 +2609,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>9276600</v>
+        <v>10771100</v>
       </c>
       <c r="E72" s="3">
+        <v>9522800</v>
+      </c>
+      <c r="F72" s="3">
         <v>8236300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>8640100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5401900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2997000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4281900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3643900</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2499,9 +2675,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2529,9 +2708,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2559,39 +2741,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>13959900</v>
+        <v>15586800</v>
       </c>
       <c r="E76" s="3">
+        <v>14206200</v>
+      </c>
+      <c r="F76" s="3">
         <v>12908400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11999900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9204100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6125500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7543100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7341100</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2619,74 +2807,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44651</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44286</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43921</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43555</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43190</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1536700</v>
+      </c>
+      <c r="E81" s="3">
         <v>2160300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-152200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3979000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3135800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-73500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1895700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1291500</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2699,38 +2896,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>860000</v>
+      </c>
+      <c r="E83" s="3">
         <v>793900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>749300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>716800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>720900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>626400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>663900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1017300</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2758,9 +2959,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2788,9 +2992,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2818,9 +3025,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2848,9 +3058,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2878,39 +3091,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3200000</v>
+      </c>
+      <c r="E89" s="3">
         <v>4875100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1848300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2139900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2503400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1618800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1532400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2424600</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2923,38 +3142,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3474500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2488400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1830600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1674200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1357000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1013600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1597100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1843800</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2982,9 +3205,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3012,39 +3238,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4287400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3610000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3667400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-979200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>611300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1260200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-940900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1974900</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3057,38 +3289,42 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>614700</v>
+      </c>
+      <c r="E96" s="3">
         <v>1251500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>634800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>732600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1162700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>808600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>959100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>972700</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3116,9 +3352,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3146,9 +3385,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3176,39 +3418,45 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1157900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1083100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1624200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1884900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1137000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-809500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-207800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2126700</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3233,40 +3481,46 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>70500</v>
+      </c>
+      <c r="E102" s="3">
         <v>182000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-194800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-724200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1977700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-450900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>383600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1677000</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3"/>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
